--- a/backtest_runs/20260410_193731/by_symbol/SMCPL/SMCPL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SMCPL/SMCPL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-967.6799999999985</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>99032.32000000001</v>
@@ -633,7 +633,7 @@
         <v>-6746.880000000014</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>99247.36</v>
@@ -679,7 +679,7 @@
         <v>-10214.39999999999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>89032.96000000001</v>
@@ -817,7 +817,7 @@
         <v>-2822.399999999992</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>97849.60000000001</v>
@@ -909,7 +909,7 @@
         <v>-4999.679999999998</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>94140.16</v>
@@ -1047,7 +1047,7 @@
         <v>-6639.359999999997</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>95537.92000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-1370.880000000014</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>103763.2</v>
@@ -1369,7 +1369,7 @@
         <v>-698.8799999999947</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>103064.32</v>
@@ -1553,7 +1553,7 @@
         <v>-26.87999999999465</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>103037.44</v>
